--- a/Planning.xlsx
+++ b/Planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hans/Repository/UAMCAntwerpen/2040FBDBIC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB711887-5E0A-CB44-9523-1D1A6020942B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4DAD14-0DBA-E548-883D-89C9C1A32A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15560" yWindow="660" windowWidth="28040" windowHeight="17180" xr2:uid="{A970DAC7-79EE-204C-A878-887588333FC0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>Les</t>
   </si>
@@ -77,6 +77,12 @@
   </si>
   <si>
     <t>Hands-on (Notebook 04)</t>
+  </si>
+  <si>
+    <t>Pharmacophore searching</t>
+  </si>
+  <si>
+    <t>Hands-on (Notebook 05)</t>
   </si>
 </sst>
 </file>
@@ -470,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB0DF1B5-948D-E147-AB80-2795254FEB89}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -556,6 +562,28 @@
         <v>11</v>
       </c>
     </row>
+    <row r="8" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Planning.xlsx
+++ b/Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hans/Repository/UAMCAntwerpen/2040FBDBIC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4DAD14-0DBA-E548-883D-89C9C1A32A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16115A1-EFC3-044D-BD5F-73C5BB912BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15560" yWindow="660" windowWidth="28040" windowHeight="17180" xr2:uid="{A970DAC7-79EE-204C-A878-887588333FC0}"/>
+    <workbookView xWindow="520" yWindow="660" windowWidth="28040" windowHeight="17180" xr2:uid="{A970DAC7-79EE-204C-A878-887588333FC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>Les</t>
   </si>
@@ -47,11 +47,6 @@
     <t>Inhoud</t>
   </si>
   <si>
-    <t>Inleiding
-Python (notebook 01)
-Proteins (notebook 02)</t>
-  </si>
-  <si>
     <t>Type les</t>
   </si>
   <si>
@@ -61,28 +56,40 @@
     <t>Hoorcollege</t>
   </si>
   <si>
-    <t>Hands-on (Notebook 02)</t>
-  </si>
-  <si>
-    <t>Hoorcollege en hands-on (Notebooks 01 and 02)</t>
-  </si>
-  <si>
     <t>Machine learning</t>
   </si>
   <si>
-    <t>Hands-on (Notebook 03)</t>
-  </si>
-  <si>
     <t>Building focussed compound databases</t>
   </si>
   <si>
-    <t>Hands-on (Notebook 04)</t>
-  </si>
-  <si>
     <t>Pharmacophore searching</t>
   </si>
   <si>
-    <t>Hands-on (Notebook 05)</t>
+    <t>Hands-on (Notebook 2)</t>
+  </si>
+  <si>
+    <t>Hands-on (Notebook 3)</t>
+  </si>
+  <si>
+    <t>Hands-on (Notebook 4)</t>
+  </si>
+  <si>
+    <t>Hands-on (Notebook 5)</t>
+  </si>
+  <si>
+    <t>Hoorcollege en hands-on (Notebook 0)</t>
+  </si>
+  <si>
+    <t>Hoorcollege en hands-on (Notebook 1)</t>
+  </si>
+  <si>
+    <t>Working with small molecules</t>
+  </si>
+  <si>
+    <t>Proteins</t>
+  </si>
+  <si>
+    <t>Inleiding en Python</t>
   </si>
 </sst>
 </file>
@@ -476,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB0DF1B5-948D-E147-AB80-2795254FEB89}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -493,40 +500,40 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>4</v>
+      <c r="B3" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -534,10 +541,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -545,10 +552,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -556,10 +563,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -567,10 +574,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -578,10 +585,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Planning.xlsx
+++ b/Planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hans/Repository/UAMCAntwerpen/2040FBDBIC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16115A1-EFC3-044D-BD5F-73C5BB912BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831F5CF8-171C-F64F-89BD-CBE28267E7C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="520" yWindow="660" windowWidth="28040" windowHeight="17180" xr2:uid="{A970DAC7-79EE-204C-A878-887588333FC0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>Les</t>
   </si>
@@ -90,6 +90,12 @@
   </si>
   <si>
     <t>Inleiding en Python</t>
+  </si>
+  <si>
+    <t>Docking</t>
+  </si>
+  <si>
+    <t>Hands-on (Notebook 6)</t>
   </si>
 </sst>
 </file>
@@ -483,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB0DF1B5-948D-E147-AB80-2795254FEB89}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -602,6 +608,28 @@
         <v>11</v>
       </c>
     </row>
+    <row r="11" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
